--- a/AAII_Financials/Quarterly/MWTCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MWTCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>MWTCY</t>
   </si>
@@ -655,72 +655,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +761,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -795,8 +802,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -833,8 +843,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +862,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,8 +901,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,8 +942,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -963,8 +983,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1001,8 +1024,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,8 +1040,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1052,8 +1079,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1090,8 +1120,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1139,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1144,8 +1178,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1182,8 +1219,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1220,8 +1260,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1258,8 +1301,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1296,8 +1342,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,8 +1383,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1372,8 +1424,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1410,8 +1465,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1547,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,8 +1629,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1600,8 +1670,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1638,8 +1711,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,8 +1752,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1714,51 +1793,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,46 +1875,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E41" s="3">
         <v>96500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>105000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>120800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>128000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>152500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>137400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>146500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>194100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>131900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1857,282 +1947,306 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>200</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>104400</v>
+      </c>
+      <c r="E43" s="3">
         <v>95700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>97700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>85900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>94000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>73000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>66100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>76300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>74000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>72700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>62400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>69100</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E44" s="3">
         <v>7900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>8100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E45" s="3">
         <v>28000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>47700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E46" s="3">
         <v>254900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>271000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>235700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>249200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>234900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>237500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>289100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>266800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>257100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>291000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>244000</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E47" s="3">
         <v>120300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>117900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>126200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>125500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>125800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>123700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>205800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>194100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>203300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>202000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>269200</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>174900</v>
+      </c>
+      <c r="E48" s="3">
         <v>162700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>157600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>170100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>173900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>173800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>166700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>173900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>163600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>168100</v>
       </c>
       <c r="M48" s="3">
         <v>168100</v>
       </c>
       <c r="N48" s="3">
+        <v>168100</v>
+      </c>
+      <c r="O48" s="3">
         <v>145100</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4133800</v>
+      </c>
+      <c r="E49" s="3">
         <v>4161200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4293700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3422400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3417200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3282300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3184000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3144800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2921700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2947300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2933900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2761000</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,46 +2324,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>218900</v>
+      </c>
+      <c r="E52" s="3">
         <v>219900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>207900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>161600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>151000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>174700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>180800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>144500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>170600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>162800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>159000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>149500</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,46 +2406,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4947600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4971500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5093900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4148200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4150100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4023900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3924600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3990000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3747100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3769600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3785000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3609700</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,236 +2483,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>343100</v>
+      </c>
+      <c r="E57" s="3">
         <v>377200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>218200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>297200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>341700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>348100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>194600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>343600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>334100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>330000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>181600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>305000</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>247200</v>
+      </c>
+      <c r="E58" s="3">
         <v>236600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>202900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>301700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>265400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>232800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>126000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>300700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>270200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>178200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>310900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>255300</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E59" s="3">
         <v>25700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>471400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>42200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>86200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>624700</v>
+      </c>
+      <c r="E60" s="3">
         <v>650100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1122600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>642400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>650400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>619500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>514100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>696000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>629800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>607900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>679100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>584500</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2389500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2460800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2042400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1624400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1679600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1703300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1713400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1545800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1512800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1559600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1489000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1281400</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>186400</v>
+      </c>
+      <c r="E62" s="3">
         <v>183300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>195600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>299200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>281900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>279300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>282500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>290600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>282300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>305800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>308500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>339700</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,46 +2850,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3329200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3418900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3478900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2673000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2714600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2694100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2593100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2605400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2486900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2523100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2519300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2236000</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,46 +3072,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1335600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1287200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1353300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1313800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1273400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1177500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1194000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1230400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1125500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1103300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1123100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1128500</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,46 +3236,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1544600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1481700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1549000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1430900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1392700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1290600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1295400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1349400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1226700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1223100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1243800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1348500</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,51 +3318,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3210,8 +3405,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,46 +3424,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E83" s="3">
         <v>22700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>20900</v>
       </c>
       <c r="H83" s="3">
         <v>20900</v>
       </c>
       <c r="I83" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J83" s="3">
         <v>17000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>19300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E89" s="3">
         <v>35700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>46800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>36300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-36000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>37200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,46 +3728,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>2200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,46 +3849,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-428600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>18500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>21900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15700</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,46 +3909,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>99400</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>95600</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>57700</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>30600</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,46 +4071,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="E100" s="3">
         <v>375200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-36200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-48000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-52100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>14100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-85100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>103000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36000</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3887,59 +4136,65 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-45000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>59400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-29600</v>
       </c>
     </row>
